--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20261021.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20261021.xlsx
@@ -755,17 +755,17 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>6,970,714</t>
+          <t>31,628,704</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -777,17 +777,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>31,628,704</t>
+          <t>6,970,714</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -799,17 +799,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>424,217,530</t>
+          <t>200,033,013</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -821,17 +821,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>200,033,013</t>
+          <t>424,217,530</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>377,600,475</t>
+          <t>316,691,708</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>316,691,708</t>
+          <t>377,600,475</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>2,254,804</t>
+          <t>7,434,928</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>7,434,928</t>
+          <t>91,571,535</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>91,571,535</t>
+          <t>2,254,804</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
